--- a/output/pdf_financials_xlsx/TNT.UN.xlsx
+++ b/output/pdf_financials_xlsx/TNT.UN.xlsx
@@ -431,6 +431,15 @@
   </sheetPr>
   <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/TNT.UN.xlsx
+++ b/output/pdf_financials_xlsx/TNT.UN.xlsx
@@ -12014,7 +12014,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>-5.765</v>
       </c>

--- a/output/pdf_financials_xlsx/TNT.UN.xlsx
+++ b/output/pdf_financials_xlsx/TNT.UN.xlsx
@@ -3101,22 +3101,22 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>7.834</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-6.111</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>13.633</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-1.352</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>1.389</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="107">
@@ -8438,7 +8438,11 @@
           <t>Change in non-cash operating working capital 15(a)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -9716,7 +9720,11 @@
           <t>Change in non-cash operating working capital 16(a)</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -10456,7 +10464,11 @@
           <t>Change in non-cash operating working capital (note 16)</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -11146,7 +11158,11 @@
           <t>Change in non-cash operating working capital (note 17)</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E167" s="5" t="n">
         <v>7.834</v>
       </c>
